--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484364_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484364_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7073</v>
+        <v>7.7013</v>
       </c>
       <c r="E2" t="n">
-        <v>8.125500000000001</v>
+        <v>8.7928</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4183</v>
+        <v>-1.0914</v>
       </c>
       <c r="G2" t="n">
         <v>7.497</v>
@@ -610,13 +610,13 @@
         <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8799</v>
+        <v>0.1142</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2642</v>
+        <v>0.9314</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1441</v>
+        <v>-0.8173</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8865</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6149</v>
+        <v>6.0764</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0366</v>
+        <v>3.2179</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4217</v>
+        <v>2.8585</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5961</v>
+        <v>4.3782</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4638</v>
+        <v>1.1545</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1323</v>
+        <v>3.2236</v>
       </c>
       <c r="J3" t="n">
-        <v>4.807</v>
+        <v>3.3842</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4833</v>
+        <v>1.3737</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3237</v>
+        <v>2.0105</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7891</v>
+        <v>0.994</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0194</v>
+        <v>-0.2192</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8085</v>
+        <v>1.2132</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5109</v>
+        <v>0.9987</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9606</v>
+        <v>0.8104</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4498</v>
+        <v>0.1883</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.4921</v>
+        <v>-0.2772</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7145</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.049</v>
+        <v>4.4796</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4901</v>
+        <v>5.1465</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5589</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3782</v>
+        <v>5.5961</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1545</v>
+        <v>4.4638</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2236</v>
+        <v>1.1323</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3842</v>
+        <v>4.807</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3737</v>
+        <v>4.4833</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0105</v>
+        <v>0.3237</v>
       </c>
       <c r="M4" t="n">
-        <v>0.994</v>
+        <v>0.7891</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2192</v>
+        <v>-0.0194</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2132</v>
+        <v>0.8085</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0286</v>
+        <v>1.3756</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08260000000000001</v>
+        <v>2.0705</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1112</v>
+        <v>-0.6949</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>-2.4921</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5884</v>
+        <v>2.7016</v>
       </c>
       <c r="E5" t="n">
-        <v>1.834</v>
+        <v>2.0561</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7544</v>
+        <v>0.6455</v>
       </c>
       <c r="G5" t="n">
         <v>1.7</v>
@@ -844,13 +844,13 @@
         <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8298</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3979</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5681</v>
+        <v>-0.677</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3321</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2431</v>
+        <v>1.8798</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1517</v>
+        <v>2.7066</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9085</v>
+        <v>-0.8268</v>
       </c>
       <c r="G6" t="n">
         <v>1.0515</v>
@@ -922,13 +922,13 @@
         <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3284</v>
+        <v>0.965</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6262</v>
+        <v>1.1811</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2978</v>
+        <v>-0.2161</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3321</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2495</v>
+        <v>1.777</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1998</v>
+        <v>-0.2093</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4493</v>
+        <v>1.9863</v>
       </c>
       <c r="G7" t="n">
         <v>0.3615</v>
@@ -1000,13 +1000,13 @@
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4973</v>
+        <v>1.0248</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0851</v>
+        <v>0.9053</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5825</v>
+        <v>0.1195</v>
       </c>
       <c r="V7" t="n">
         <v>-0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5964</v>
+        <v>0.0192</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8256</v>
+        <v>1.1688</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.422</v>
+        <v>-1.1497</v>
       </c>
       <c r="G8" t="n">
         <v>3.0694</v>
@@ -1078,13 +1078,13 @@
         <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7016</v>
+        <v>1.3172</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2163</v>
+        <v>1.5595</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5147</v>
+        <v>-0.2423</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8279</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9414</v>
+        <v>-1.6177</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0062</v>
+        <v>-1.4919</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0648</v>
+        <v>-0.1258</v>
       </c>
       <c r="G9" t="n">
         <v>-1.055</v>
@@ -1156,13 +1156,13 @@
         <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4494</v>
+        <v>0.7731</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9383</v>
+        <v>0.4527</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5111</v>
+        <v>0.3205</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5545</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.301</v>
+        <v>-2.1933</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0586</v>
+        <v>-2.9781</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9699</v>
@@ -1234,13 +1234,13 @@
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4969</v>
+        <v>0.6046</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8173</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3204</v>
+        <v>-0.2931</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>19.6134</v>
+        <v>20.8239</v>
       </c>
       <c r="E11" t="n">
-        <v>17.1989</v>
+        <v>18.4094</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4145</v>
+        <v>2.4146</v>
       </c>
       <c r="G11" t="n">
         <v>20.6288</v>
       </c>
       <c r="H11" t="n">
-        <v>7.1387</v>
+        <v>7.138700000000001</v>
       </c>
       <c r="I11" t="n">
         <v>13.4899</v>
@@ -1312,19 +1312,19 @@
         <v>11.7205</v>
       </c>
       <c r="S11" t="n">
-        <v>6.9058</v>
+        <v>8.116199999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>9.218299999999999</v>
+        <v>10.4286</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.3125</v>
+        <v>-2.3124</v>
       </c>
       <c r="V11" t="n">
-        <v>-7.920999999999999</v>
+        <v>-7.921000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>4.268199999999999</v>
+        <v>4.2682</v>
       </c>
       <c r="X11" t="n">
         <v>-12.1893</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.8094</v>
+        <v>3.8574</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0157</v>
+        <v>3.7123</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2063</v>
+        <v>0.1451</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6079</v>
@@ -1390,13 +1390,13 @@
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2619</v>
+        <v>-0.2139</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6824</v>
+        <v>0.3791</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9444</v>
+        <v>-0.593</v>
       </c>
       <c r="V12" t="n">
         <v>5.4838</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2702</v>
+        <v>0.1396</v>
       </c>
       <c r="E13" t="n">
-        <v>3.306</v>
+        <v>2.396</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0358</v>
+        <v>-2.2564</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8695</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1946</v>
+        <v>0.064</v>
       </c>
       <c r="T13" t="n">
-        <v>1.574</v>
+        <v>0.664</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3794</v>
+        <v>-0.6</v>
       </c>
       <c r="V13" t="n">
         <v>1.7731</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3427</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7951</v>
+        <v>1.2744</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4525</v>
+        <v>-1.2843</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4743</v>
+        <v>0.5948</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8788</v>
+        <v>-1.2123</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4045</v>
+        <v>1.8071</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6741</v>
+        <v>1.299</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6741</v>
+        <v>-0.5091</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.8081</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1998</v>
+        <v>-0.7042</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2047</v>
+        <v>-0.7032</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4045</v>
+        <v>-0.001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1772</v>
+        <v>-1.1404</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.121</v>
+        <v>-0.0246</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0561</v>
+        <v>-1.1158</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2772</v>
+        <v>-0.8317</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0751</v>
+        <v>-0.3155</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3471</v>
+        <v>-0.7951</v>
       </c>
       <c r="F15" t="n">
-        <v>0.272</v>
+        <v>0.4797</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1799</v>
+        <v>-0.4743</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2251</v>
+        <v>-0.8788</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4051</v>
+        <v>0.4045</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3697</v>
+        <v>-0.6741</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3697</v>
+        <v>-0.6741</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5496</v>
+        <v>0.1998</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1445</v>
+        <v>-0.2047</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4051</v>
+        <v>0.4045</v>
       </c>
       <c r="P15" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.1721</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.618</v>
+        <v>-0.15</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5447</v>
+        <v>-0.121</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0733</v>
+        <v>-0.0289</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2772</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2505</v>
+        <v>-0.5968</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4655</v>
+        <v>-0.8415</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.716</v>
+        <v>0.2448</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5948</v>
+        <v>-0.1799</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2123</v>
+        <v>0.2251</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8071</v>
+        <v>-0.4051</v>
       </c>
       <c r="J16" t="n">
-        <v>1.299</v>
+        <v>0.3697</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5091</v>
+        <v>0.3697</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8081</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7042</v>
+        <v>-0.5496</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7032</v>
+        <v>-0.1445</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.001</v>
+        <v>-0.4051</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.3811</v>
+        <v>-0.1396</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8335</v>
+        <v>-0.0391</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.5475</v>
+        <v>-0.1005</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8317</v>
+        <v>-0.2772</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8317</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.5905</v>
+        <v>-3.1911</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.22</v>
+        <v>-0.1189</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.3705</v>
+        <v>-3.0722</v>
       </c>
       <c r="G17" t="n">
         <v>-3.2927</v>
@@ -1780,13 +1780,13 @@
         <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2309</v>
+        <v>-0.8316</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0497</v>
+        <v>0.1508</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2806</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>2.1052</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.8487</v>
+        <v>-3.7929</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1978</v>
+        <v>-1.6023</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6509</v>
+        <v>-2.1906</v>
       </c>
       <c r="G18" t="n">
         <v>-2.847</v>
@@ -1858,13 +1858,13 @@
         <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3571</v>
+        <v>-0.3013</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4584</v>
+        <v>1.0539</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.8155</v>
+        <v>-1.3552</v>
       </c>
       <c r="V18" t="n">
         <v>0.3321</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.4092</v>
+        <v>-5.8824</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1111</v>
+        <v>-1.7178</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.2981</v>
+        <v>-4.1646</v>
       </c>
       <c r="G19" t="n">
         <v>-4.1974</v>
@@ -1936,13 +1936,13 @@
         <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4072</v>
+        <v>-0.8804</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8532</v>
+        <v>0.2465</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2603</v>
+        <v>-1.1269</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6093</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-9.176299999999999</v>
+        <v>-7.7995</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.1984</v>
+        <v>-4.3895</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.9779</v>
+        <v>-3.41</v>
       </c>
       <c r="G20" t="n">
         <v>-5.7548</v>
@@ -2014,13 +2014,13 @@
         <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6672</v>
+        <v>-1.2904</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.806</v>
+        <v>0.0029</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.8612</v>
+        <v>-1.2933</v>
       </c>
       <c r="V20" t="n">
         <v>0.2224</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-19.6134</v>
+        <v>-17.5911</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0823</v>
+        <v>-2.0824</v>
       </c>
       <c r="F21" t="n">
-        <v>-17.531</v>
+        <v>-15.5085</v>
       </c>
       <c r="G21" t="n">
         <v>-20.6287</v>
@@ -2065,7 +2065,7 @@
         <v>-13.4899</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.195600000000001</v>
+        <v>-5.1956</v>
       </c>
       <c r="K21" t="n">
         <v>2.890699999999999</v>
@@ -2083,7 +2083,7 @@
         <v>-5.4037</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>-3.33066907387547e-16</v>
       </c>
       <c r="Q21" t="n">
         <v>-11.7207</v>
@@ -2092,13 +2092,13 @@
         <v>11.7206</v>
       </c>
       <c r="S21" t="n">
-        <v>-6.906000000000001</v>
+        <v>-4.883599999999999</v>
       </c>
       <c r="T21" t="n">
         <v>2.3125</v>
       </c>
       <c r="U21" t="n">
-        <v>-9.218299999999999</v>
+        <v>-7.196</v>
       </c>
       <c r="V21" t="n">
         <v>7.9212</v>
@@ -2107,7 +2107,7 @@
         <v>12.5212</v>
       </c>
       <c r="X21" t="n">
-        <v>-4.600099999999999</v>
+        <v>-4.6001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484364_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484364_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7016</v>
+        <v>1.8798</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0561</v>
+        <v>2.7066</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6455</v>
+        <v>-0.8268</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7</v>
+        <v>1.0515</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1175</v>
+        <v>-0.7017</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4175</v>
+        <v>1.7533</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1904</v>
+        <v>1.0063</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4162</v>
+        <v>-0.3428</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2258</v>
+        <v>1.3492</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.0452</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2988</v>
+        <v>-0.3589</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8083</v>
+        <v>0.4041</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.965</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.1811</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.677</v>
+        <v>-0.2161</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3321</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2224</v>
+        <v>1.4959</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5545</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +902,72 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8798</v>
+        <v>1.7876</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7066</v>
+        <v>1.1421</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8268</v>
+        <v>0.6455</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0515</v>
+        <v>0.786</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7017</v>
+        <v>1.8105</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7533</v>
+        <v>-1.0245</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0063</v>
+        <v>0.2764</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3428</v>
+        <v>2.1092</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3492</v>
+        <v>-1.8328</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0452</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3589</v>
+        <v>-0.2988</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4041</v>
+        <v>0.8083</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>0.965</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1811</v>
+        <v>1.62</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2161</v>
+        <v>-0.677</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3321</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4959</v>
+        <v>0.2224</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8279</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0192</v>
+        <v>0.914</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1688</v>
+        <v>0.914</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1497</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.0694</v>
+        <v>0.914</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2371</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8322</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6296</v>
+        <v>0.914</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7406</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8891</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4397</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5034</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9431</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.5395</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3172</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5595</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2423</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6177</v>
+        <v>0.0192</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4919</v>
+        <v>1.1688</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1258</v>
+        <v>-1.1497</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.055</v>
+        <v>3.0694</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9044</v>
+        <v>0.2371</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8494</v>
+        <v>2.8322</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2451</v>
+        <v>2.6296</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2855</v>
+        <v>0.7406</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>1.8891</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1901</v>
+        <v>0.4397</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6188</v>
+        <v>-0.5034</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8089</v>
+        <v>0.9431</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7814</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7731</v>
+        <v>1.3172</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4527</v>
+        <v>1.5595</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3205</v>
+        <v>-0.2423</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5545</v>
+        <v>-1.8279</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8317</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1933</v>
+        <v>-1.6177</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9781</v>
+        <v>-1.4919</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7848000000000001</v>
+        <v>-0.1258</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9699</v>
+        <v>-1.055</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3735</v>
+        <v>-1.9044</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3435</v>
+        <v>0.8494</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8991</v>
+        <v>-1.2451</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6577</v>
+        <v>-1.2855</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.5568</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9292</v>
+        <v>0.1901</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2842</v>
+        <v>-0.6188</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2134</v>
+        <v>0.8089</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6046</v>
+        <v>0.7731</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.4527</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2931</v>
+        <v>0.3205</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>20.8239</v>
+        <v>-2.1933</v>
       </c>
       <c r="E11" t="n">
-        <v>18.4094</v>
+        <v>-2.9781</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4146</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>20.6288</v>
+        <v>-1.9699</v>
       </c>
       <c r="H11" t="n">
-        <v>7.138700000000001</v>
+        <v>1.3735</v>
       </c>
       <c r="I11" t="n">
-        <v>13.4899</v>
+        <v>-3.3435</v>
       </c>
       <c r="J11" t="n">
-        <v>15.4329</v>
+        <v>-2.8991</v>
       </c>
       <c r="K11" t="n">
-        <v>10.0294</v>
+        <v>1.6577</v>
       </c>
       <c r="L11" t="n">
-        <v>5.403799999999999</v>
+        <v>-4.5568</v>
       </c>
       <c r="M11" t="n">
-        <v>5.1958</v>
+        <v>0.9292</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.8905</v>
+        <v>-0.2842</v>
       </c>
       <c r="O11" t="n">
-        <v>8.086200000000002</v>
+        <v>1.2134</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0001000000000000445</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-11.7205</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>11.7205</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>8.116199999999999</v>
+        <v>0.6046</v>
       </c>
       <c r="T11" t="n">
-        <v>10.4286</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.3124</v>
+        <v>-0.2931</v>
       </c>
       <c r="V11" t="n">
-        <v>-7.921000000000001</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>4.2682</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-12.1893</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.8574</v>
+        <v>20.82389999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7123</v>
+        <v>18.40939999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1451</v>
+        <v>2.414600000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6079</v>
+        <v>20.6288</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2589</v>
+        <v>7.138700000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.349</v>
+        <v>13.4899</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9785</v>
+        <v>15.4329</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3697</v>
+        <v>10.0294</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3482</v>
+        <v>5.403799999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6293</v>
+        <v>5.195799999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-2.8905</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0008</v>
+        <v>8.0862</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1953</v>
+        <v>-9.999999999993348e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1721</v>
+        <v>-11.7205</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>11.7205</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2139</v>
+        <v>8.116200000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3791</v>
+        <v>10.4286</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.593</v>
+        <v>-2.3124</v>
       </c>
       <c r="V12" t="n">
-        <v>5.4838</v>
+        <v>-7.920999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>5.4838</v>
+        <v>4.268199999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
-      </c>
+        <v>-12.1893</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1396</v>
+        <v>3.5504</v>
       </c>
       <c r="E13" t="n">
-        <v>2.396</v>
+        <v>3.4053</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2564</v>
+        <v>0.1451</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.8695</v>
+        <v>-1.9149</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2714</v>
+        <v>-0.5659</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.1409</v>
+        <v>-1.349</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07240000000000001</v>
+        <v>-1.2855</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7283</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6559</v>
+        <v>-1.3482</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.9419</v>
+        <v>-0.6293</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4569</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.485</v>
+        <v>-0.0008</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>0.064</v>
+        <v>-0.2139</v>
       </c>
       <c r="T13" t="n">
-        <v>0.664</v>
+        <v>0.3791</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6</v>
+        <v>-0.593</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7731</v>
+        <v>5.4838</v>
       </c>
       <c r="W13" t="n">
-        <v>2.0503</v>
+        <v>5.4838</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2744</v>
+        <v>0.307</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2843</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5948</v>
+        <v>0.307</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2123</v>
+        <v>0.307</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8071</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.299</v>
+        <v>0.307</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5091</v>
+        <v>0.307</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8081</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7042</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7032</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1404</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0246</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1158</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3155</v>
+        <v>0.307</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7951</v>
+        <v>0.307</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4797</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4743</v>
+        <v>0.307</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8788</v>
+        <v>0.307</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4045</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6741</v>
+        <v>0.307</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6741</v>
+        <v>0.307</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1998</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4045</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0289</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5968</v>
+        <v>0.1396</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8415</v>
+        <v>2.396</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2448</v>
+        <v>-2.2564</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1799</v>
+        <v>-2.8695</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2251</v>
+        <v>1.2714</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4051</v>
+        <v>-4.1409</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3697</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3697</v>
+        <v>2.7283</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-2.6559</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5496</v>
+        <v>-2.9419</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1445</v>
+        <v>-1.4569</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4051</v>
+        <v>-1.485</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1396</v>
+        <v>0.064</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0391</v>
+        <v>0.664</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1005</v>
+        <v>-0.6</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>1.7731</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.0503</v>
       </c>
       <c r="X16" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.1911</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1189</v>
+        <v>1.2744</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0722</v>
+        <v>-1.2843</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.2927</v>
+        <v>0.5948</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9859</v>
+        <v>-1.2123</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.3067</v>
+        <v>1.8071</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8354</v>
+        <v>1.299</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3914</v>
+        <v>-0.5091</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2268</v>
+        <v>1.8081</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4573</v>
+        <v>-0.7042</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3773</v>
+        <v>-0.7032</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0799</v>
+        <v>-0.001</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8316</v>
+        <v>-1.1404</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1508</v>
+        <v>-0.0246</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-1.1158</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1052</v>
+        <v>-0.8317</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7929</v>
+        <v>-0.3155</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6023</v>
+        <v>-0.7951</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1906</v>
+        <v>0.4797</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.847</v>
+        <v>-0.4743</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7693</v>
+        <v>-0.8788</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0778</v>
+        <v>0.4045</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5894</v>
+        <v>-0.6741</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.6741</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2673</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2577</v>
+        <v>0.1998</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4472</v>
+        <v>-0.2047</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8105</v>
+        <v>0.4045</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3013</v>
+        <v>-0.15</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0539</v>
+        <v>-0.121</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3552</v>
+        <v>-0.0289</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.8824</v>
+        <v>-0.5968</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7178</v>
+        <v>-0.8415</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.1646</v>
+        <v>0.2448</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.1974</v>
+        <v>-0.1799</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8115</v>
+        <v>0.2251</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.3859</v>
+        <v>-0.4051</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5067</v>
+        <v>0.3697</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3942</v>
+        <v>0.3697</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9009</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.6907</v>
+        <v>-0.5496</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.2057</v>
+        <v>-0.1445</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.485</v>
+        <v>-0.4051</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3441</v>
+        <v>-1.1721</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8804</v>
+        <v>-0.1396</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2465</v>
+        <v>-0.0391</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1269</v>
+        <v>-0.1005</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.7995</v>
+        <v>-3.1911</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3895</v>
+        <v>-0.1189</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.41</v>
+        <v>-3.0722</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.7548</v>
+        <v>-3.2927</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.7186</v>
+        <v>-0.9859</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0361</v>
+        <v>-2.3067</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.3526</v>
+        <v>-0.8354</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.8573</v>
+        <v>0.3914</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4953</v>
+        <v>-1.2268</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4022</v>
+        <v>-2.4573</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8613</v>
+        <v>-1.3773</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5409</v>
+        <v>-1.0799</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2904</v>
+        <v>-0.8316</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0029</v>
+        <v>0.1508</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2933</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2224</v>
+        <v>2.1052</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1089</v>
+        <v>2.7145</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8865</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,68 +2143,318 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>-4.0999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.9093</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-2.1906</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-3.154</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.0762</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-2.0778</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.8963</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1.2673</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-2.2577</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1.4472</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.8105</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.3013</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.0539</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.3552</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S. ESTEVES-GARCIA COFFI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-5.8824</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.7178</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-4.1646</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-4.1974</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.8115</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-3.3859</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.5067</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.3942</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-1.9009</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-3.6907</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-2.2057</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1.485</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.8804</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-1.1269</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A. BARQUETS ARIZA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-7.7995</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-4.3895</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-5.7548</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-3.7186</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-2.0361</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-3.3526</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.8573</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.4953</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-2.4022</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.8613</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.5409</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-1.2904</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-1.2933</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.1089</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484364_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>-17.5911</v>
       </c>
-      <c r="E21" t="n">
-        <v>-2.0824</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="E24" t="n">
+        <v>-2.082399999999999</v>
+      </c>
+      <c r="F24" t="n">
         <v>-15.5085</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G24" t="n">
         <v>-20.6287</v>
       </c>
-      <c r="H21" t="n">
-        <v>-7.1388</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="H24" t="n">
+        <v>-7.1387</v>
+      </c>
+      <c r="I24" t="n">
         <v>-13.4899</v>
       </c>
-      <c r="J21" t="n">
-        <v>-5.1956</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="J24" t="n">
+        <v>-5.1955</v>
+      </c>
+      <c r="K24" t="n">
         <v>2.890699999999999</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L24" t="n">
         <v>-8.0863</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M24" t="n">
         <v>-15.4331</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N24" t="n">
         <v>-10.0293</v>
       </c>
-      <c r="O21" t="n">
-        <v>-5.4037</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="O24" t="n">
+        <v>-5.403700000000001</v>
+      </c>
+      <c r="P24" t="n">
         <v>-3.33066907387547e-16</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q24" t="n">
         <v>-11.7207</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R24" t="n">
         <v>11.7206</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S24" t="n">
         <v>-4.883599999999999</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T24" t="n">
         <v>2.3125</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U24" t="n">
         <v>-7.196</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V24" t="n">
         <v>7.9212</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W24" t="n">
         <v>12.5212</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X24" t="n">
         <v>-4.6001</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
